--- a/salidas/empresas/AMGN.xlsx
+++ b/salidas/empresas/AMGN.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>48.64817047119141</v>
+        <v>48.64816284179688</v>
       </c>
       <c r="C2" t="n">
         <v>72.88999938964844</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>50.37677764892578</v>
+        <v>50.37677383422852</v>
       </c>
       <c r="C3" t="n">
         <v>75.48000335693359</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>48.55471038818359</v>
+        <v>48.55471801757812</v>
       </c>
       <c r="C4" t="n">
         <v>72.75</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>45.18424987792969</v>
+        <v>45.18425369262695</v>
       </c>
       <c r="C5" t="n">
         <v>67.69999694824219</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>45.1108512878418</v>
+        <v>45.11083984375</v>
       </c>
       <c r="C6" t="n">
         <v>67.58999633789062</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>43.53573989868164</v>
+        <v>43.53573226928711</v>
       </c>
       <c r="C7" t="n">
         <v>65.23000335693359</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>46.52577590942383</v>
+        <v>46.52575302124023</v>
       </c>
       <c r="C8" t="n">
         <v>69.70999908447266</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>45.40451049804688</v>
+        <v>45.40450668334961</v>
       </c>
       <c r="C9" t="n">
         <v>68.02999877929688</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>47.74048233032227</v>
+        <v>47.74046325683594</v>
       </c>
       <c r="C10" t="n">
         <v>71.52999877929688</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>50.66377258300781</v>
+        <v>50.66376495361328</v>
       </c>
       <c r="C11" t="n">
         <v>75.91000366210938</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>47.41343307495117</v>
+        <v>47.41344451904297</v>
       </c>
       <c r="C12" t="n">
         <v>71.04000091552734</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>45.59136581420898</v>
+        <v>45.59138107299805</v>
       </c>
       <c r="C13" t="n">
         <v>68.30999755859375</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>46.96627426147461</v>
+        <v>46.96626281738281</v>
       </c>
       <c r="C14" t="n">
         <v>70.37000274658203</v>
@@ -729,7 +741,7 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>37.29536819458008</v>
+        <v>37.29536056518555</v>
       </c>
       <c r="C16" t="n">
         <v>55.88000106811523</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>42.80825042724609</v>
+        <v>42.8082389831543</v>
       </c>
       <c r="C17" t="n">
         <v>64.13999938964844</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>37.67580413818359</v>
+        <v>37.67579650878906</v>
       </c>
       <c r="C18" t="n">
         <v>56.45000076293945</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>36.9015998840332</v>
+        <v>36.90158081054688</v>
       </c>
       <c r="C19" t="n">
         <v>55.29000091552734</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>35.86709594726562</v>
+        <v>35.86708450317383</v>
       </c>
       <c r="C20" t="n">
         <v>53.7400016784668</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>33.44436645507812</v>
+        <v>33.44435882568359</v>
       </c>
       <c r="C21" t="n">
         <v>50.11000061035156</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>37.75588226318359</v>
+        <v>37.75588607788086</v>
       </c>
       <c r="C22" t="n">
         <v>56.56999969482422</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>38.78371047973633</v>
+        <v>38.7837028503418</v>
       </c>
       <c r="C23" t="n">
         <v>58.11000061035156</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>36.87490081787109</v>
+        <v>36.87489700317383</v>
       </c>
       <c r="C24" t="n">
         <v>55.25</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>30.99492073059082</v>
+        <v>30.99492263793945</v>
       </c>
       <c r="C25" t="n">
         <v>46.43999862670898</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>31.09506225585938</v>
+        <v>31.09504318237305</v>
       </c>
       <c r="C26" t="n">
         <v>46.59000015258789</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>30.38091087341309</v>
+        <v>30.38089752197266</v>
       </c>
       <c r="C27" t="n">
         <v>45.52000045776367</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>27.88477325439453</v>
+        <v>27.88474464416504</v>
       </c>
       <c r="C28" t="n">
         <v>41.77999877929688</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>27.9448299407959</v>
+        <v>27.94482612609863</v>
       </c>
       <c r="C29" t="n">
         <v>41.86999893188477</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>29.38645362854004</v>
+        <v>29.38646125793457</v>
       </c>
       <c r="C30" t="n">
         <v>44.02999877929688</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>31.4754810333252</v>
+        <v>31.47546195983887</v>
       </c>
       <c r="C31" t="n">
         <v>47.15999984741211</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>41.80044937133789</v>
+        <v>41.80045318603516</v>
       </c>
       <c r="C32" t="n">
         <v>62.63000106811523</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>41.947265625</v>
+        <v>41.94728469848633</v>
       </c>
       <c r="C33" t="n">
         <v>62.84999847412109</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>39.55791091918945</v>
+        <v>39.55790710449219</v>
       </c>
       <c r="C34" t="n">
         <v>59.27000045776367</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>39.97170639038086</v>
+        <v>39.97171020507812</v>
       </c>
       <c r="C35" t="n">
         <v>59.88999938964844</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>37.06843185424805</v>
+        <v>37.06845092773438</v>
       </c>
       <c r="C36" t="n">
         <v>55.54000091552734</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>38.54344940185547</v>
+        <v>38.54343032836914</v>
       </c>
       <c r="C37" t="n">
         <v>57.75</v>
@@ -1166,7 +1178,7 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>32.65682601928711</v>
+        <v>32.65680694580078</v>
       </c>
       <c r="C39" t="n">
         <v>48.93000030517578</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>33.05058288574219</v>
+        <v>33.05058670043945</v>
       </c>
       <c r="C40" t="n">
         <v>49.52000045776367</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>32.34980010986328</v>
+        <v>32.34979629516602</v>
       </c>
       <c r="C41" t="n">
         <v>48.47000122070312</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>33.33089447021484</v>
+        <v>33.33090209960938</v>
       </c>
       <c r="C42" t="n">
         <v>49.93999862670898</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>35.33315277099609</v>
+        <v>35.33314895629883</v>
       </c>
       <c r="C43" t="n">
         <v>52.93999862670898</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>41.58687210083008</v>
+        <v>41.58686447143555</v>
       </c>
       <c r="C44" t="n">
         <v>62.31000137329102</v>
@@ -1299,7 +1311,7 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
@@ -1324,11 +1336,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>40.19862365722656</v>
+        <v>40.19863891601562</v>
       </c>
       <c r="C46" t="n">
         <v>60.22999954223633</v>
@@ -1349,7 +1361,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
@@ -1374,11 +1386,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>37.60906982421875</v>
+        <v>37.60905075073242</v>
       </c>
       <c r="C48" t="n">
         <v>56.34999847412109</v>
@@ -1399,11 +1411,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>37.75588226318359</v>
+        <v>37.75588607788086</v>
       </c>
       <c r="C49" t="n">
         <v>56.56999969482422</v>
@@ -1424,7 +1436,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
@@ -1449,11 +1461,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>37.7825927734375</v>
+        <v>37.78258514404297</v>
       </c>
       <c r="C51" t="n">
         <v>56.61000061035156</v>
@@ -1474,11 +1486,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>39.93833923339844</v>
+        <v>39.9383430480957</v>
       </c>
       <c r="C52" t="n">
         <v>59.84000015258789</v>
@@ -1499,11 +1511,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>38.24978637695312</v>
+        <v>38.24978256225586</v>
       </c>
       <c r="C53" t="n">
         <v>57.31000137329102</v>
@@ -1524,11 +1536,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>34.5589485168457</v>
+        <v>34.55895233154297</v>
       </c>
       <c r="C54" t="n">
         <v>51.77999877929688</v>
@@ -1549,11 +1561,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>35.10622787475586</v>
+        <v>35.10624694824219</v>
       </c>
       <c r="C55" t="n">
         <v>52.59999847412109</v>
@@ -1574,11 +1586,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>36.39435195922852</v>
+        <v>36.39434814453125</v>
       </c>
       <c r="C56" t="n">
         <v>54.52999877929688</v>
@@ -1599,11 +1611,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>34.06505966186523</v>
+        <v>34.06506729125977</v>
       </c>
       <c r="C57" t="n">
         <v>51.04000091552734</v>
@@ -1624,11 +1636,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>36.78145599365234</v>
+        <v>36.78145980834961</v>
       </c>
       <c r="C58" t="n">
         <v>55.11000061035156</v>
@@ -1649,11 +1661,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>38.16967391967773</v>
+        <v>38.169677734375</v>
       </c>
       <c r="C59" t="n">
         <v>57.18999862670898</v>
@@ -1674,11 +1686,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>35.16629409790039</v>
+        <v>35.16628646850586</v>
       </c>
       <c r="C60" t="n">
         <v>52.68999862670898</v>
@@ -1699,11 +1711,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>36.64131164550781</v>
+        <v>36.64130401611328</v>
       </c>
       <c r="C61" t="n">
         <v>54.90000152587891</v>
@@ -1724,11 +1736,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>36.76142883300781</v>
+        <v>36.76143646240234</v>
       </c>
       <c r="C62" t="n">
         <v>55.08000183105469</v>
@@ -1749,11 +1761,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>34.25860595703125</v>
+        <v>34.25859069824219</v>
       </c>
       <c r="C63" t="n">
         <v>51.33000183105469</v>
@@ -1778,11 +1790,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>35.67352294921875</v>
+        <v>35.67353439331055</v>
       </c>
       <c r="C64" t="n">
         <v>53.45000076293945</v>
@@ -1807,11 +1819,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>37.9427490234375</v>
+        <v>37.94275665283203</v>
       </c>
       <c r="C65" t="n">
         <v>56.84999847412109</v>
@@ -1836,11 +1848,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>40.40555191040039</v>
+        <v>40.40552139282227</v>
       </c>
       <c r="C66" t="n">
         <v>60.54000091552734</v>
@@ -1865,11 +1877,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>38.94390106201172</v>
+        <v>38.94390869140625</v>
       </c>
       <c r="C67" t="n">
         <v>58.34999847412109</v>
@@ -1894,11 +1906,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>36.50780868530273</v>
+        <v>36.50780487060547</v>
       </c>
       <c r="C68" t="n">
         <v>54.70000076293945</v>
@@ -1923,11 +1935,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>37.17673492431641</v>
+        <v>37.17673873901367</v>
       </c>
       <c r="C69" t="n">
         <v>55.40000152587891</v>
@@ -1952,11 +1964,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>36.88147354125977</v>
+        <v>36.88147735595703</v>
       </c>
       <c r="C70" t="n">
         <v>54.95999908447266</v>
@@ -1981,11 +1993,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>38.4316291809082</v>
+        <v>38.43161773681641</v>
       </c>
       <c r="C71" t="n">
         <v>57.27000045776367</v>
@@ -2010,11 +2022,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>39.05183410644531</v>
+        <v>39.05183029174805</v>
       </c>
       <c r="C72" t="n">
         <v>57.90999984741211</v>
@@ -2039,11 +2051,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>43.30023956298828</v>
+        <v>43.30025482177734</v>
       </c>
       <c r="C73" t="n">
         <v>64.20999908447266</v>
@@ -2068,11 +2080,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>45.80884552001953</v>
+        <v>45.80885696411133</v>
       </c>
       <c r="C74" t="n">
         <v>67.93000030517578</v>
@@ -2097,11 +2109,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>46.10922622680664</v>
+        <v>46.10923385620117</v>
       </c>
       <c r="C75" t="n">
         <v>68.01000213623047</v>
@@ -2126,11 +2138,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>46.08211898803711</v>
+        <v>46.08211517333984</v>
       </c>
       <c r="C76" t="n">
         <v>67.97000122070312</v>
@@ -2155,11 +2167,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>48.21095657348633</v>
+        <v>48.2109489440918</v>
       </c>
       <c r="C77" t="n">
         <v>71.11000061035156</v>
@@ -2184,11 +2196,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>47.37392425537109</v>
+        <v>47.37392807006836</v>
       </c>
       <c r="C78" t="n">
         <v>69.51999664306641</v>
@@ -2213,11 +2225,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>49.68402862548828</v>
+        <v>49.68399810791016</v>
       </c>
       <c r="C79" t="n">
         <v>72.91000366210938</v>
@@ -2242,11 +2254,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>56.28719711303711</v>
+        <v>56.28723526000977</v>
       </c>
       <c r="C80" t="n">
         <v>82.59999847412109</v>
@@ -2271,11 +2283,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>57.43816757202148</v>
+        <v>57.43815994262695</v>
       </c>
       <c r="C81" t="n">
         <v>83.91999816894531</v>
@@ -2300,11 +2312,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>57.69142150878906</v>
+        <v>57.6914176940918</v>
       </c>
       <c r="C82" t="n">
         <v>84.29000091552734</v>
@@ -2329,11 +2341,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>59.19716262817383</v>
+        <v>59.19716644287109</v>
       </c>
       <c r="C83" t="n">
         <v>86.48999786376953</v>
@@ -2358,11 +2370,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>61.03516387939453</v>
+        <v>61.03513717651367</v>
       </c>
       <c r="C84" t="n">
         <v>88.80000305175781</v>
@@ -2387,11 +2399,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>59.24809646606445</v>
+        <v>59.24808502197266</v>
       </c>
       <c r="C85" t="n">
         <v>86.19999694824219</v>
@@ -2416,11 +2428,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>58.73949432373047</v>
+        <v>58.73948287963867</v>
       </c>
       <c r="C86" t="n">
         <v>85.45999908447266</v>
@@ -2445,11 +2457,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>63.26803207397461</v>
+        <v>63.26802444458008</v>
       </c>
       <c r="C87" t="n">
         <v>91.55000305175781</v>
@@ -2474,11 +2486,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>70.84226226806641</v>
+        <v>70.84222412109375</v>
       </c>
       <c r="C88" t="n">
         <v>102.5100021362305</v>
@@ -2503,7 +2515,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
@@ -2532,11 +2544,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>69.78072357177734</v>
+        <v>69.78073883056641</v>
       </c>
       <c r="C90" t="n">
         <v>100.5299987792969</v>
@@ -2561,11 +2573,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>68.48271942138672</v>
+        <v>68.48269653320312</v>
       </c>
       <c r="C91" t="n">
         <v>98.66000366210938</v>
@@ -2590,11 +2602,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>75.16712951660156</v>
+        <v>75.16713714599609</v>
       </c>
       <c r="C92" t="n">
         <v>108.2900009155273</v>
@@ -2619,11 +2631,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>75.94931030273438</v>
+        <v>75.94929504394531</v>
       </c>
       <c r="C93" t="n">
         <v>108.9400024414062</v>
@@ -2648,11 +2660,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>78.02685546875</v>
+        <v>78.02684783935547</v>
       </c>
       <c r="C94" t="n">
         <v>111.9199981689453</v>
@@ -2677,7 +2689,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
@@ -2706,11 +2718,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>79.86441040039062</v>
+        <v>79.86439514160156</v>
       </c>
       <c r="C96" t="n">
         <v>114.0800018310547</v>
@@ -2735,11 +2747,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>79.86441040039062</v>
+        <v>79.86439514160156</v>
       </c>
       <c r="C97" t="n">
         <v>114.0800018310547</v>
@@ -2764,11 +2776,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>83.27375793457031</v>
+        <v>83.27376556396484</v>
       </c>
       <c r="C98" t="n">
         <v>118.9499969482422</v>
@@ -2793,11 +2805,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>87.26564788818359</v>
+        <v>87.26565551757812</v>
       </c>
       <c r="C99" t="n">
         <v>124.0199966430664</v>
@@ -2822,11 +2834,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>86.78716278076172</v>
+        <v>86.78715515136719</v>
       </c>
       <c r="C100" t="n">
         <v>123.3399963378906</v>
@@ -2851,7 +2863,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
@@ -2880,11 +2892,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>82.06343841552734</v>
+        <v>82.06344604492188</v>
       </c>
       <c r="C102" t="n">
         <v>115.9899978637695</v>
@@ -2909,11 +2921,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>83.74728393554688</v>
+        <v>83.74730682373047</v>
       </c>
       <c r="C103" t="n">
         <v>118.370002746582</v>
@@ -2938,11 +2950,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>90.12900543212891</v>
+        <v>90.12899017333984</v>
       </c>
       <c r="C104" t="n">
         <v>127.3899993896484</v>
@@ -2967,11 +2979,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>99.08668518066406</v>
+        <v>99.08670043945312</v>
       </c>
       <c r="C105" t="n">
         <v>139.3800048828125</v>
@@ -2996,11 +3008,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>99.85450744628906</v>
+        <v>99.85446929931641</v>
       </c>
       <c r="C106" t="n">
         <v>140.4600067138672</v>
@@ -3025,11 +3037,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>115.2954330444336</v>
+        <v>115.2954635620117</v>
       </c>
       <c r="C107" t="n">
         <v>162.1799926757812</v>
@@ -3054,11 +3066,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>117.9696578979492</v>
+        <v>117.9696350097656</v>
       </c>
       <c r="C108" t="n">
         <v>165.3099975585938</v>
@@ -3083,11 +3095,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>113.6735992431641</v>
+        <v>113.6735763549805</v>
       </c>
       <c r="C109" t="n">
         <v>159.2899932861328</v>
@@ -3112,11 +3124,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>108.6568222045898</v>
+        <v>108.6568298339844</v>
       </c>
       <c r="C110" t="n">
         <v>152.2599945068359</v>
@@ -3141,11 +3153,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>113.1491165161133</v>
+        <v>113.1491088867188</v>
       </c>
       <c r="C111" t="n">
         <v>157.7200012207031</v>
@@ -3170,7 +3182,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
@@ -3199,11 +3211,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>113.285400390625</v>
+        <v>113.2853927612305</v>
       </c>
       <c r="C113" t="n">
         <v>157.9100036621094</v>
@@ -3228,11 +3240,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>112.6542892456055</v>
+        <v>112.6542587280273</v>
       </c>
       <c r="C114" t="n">
         <v>156.2599945068359</v>
@@ -3257,11 +3269,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>110.6789016723633</v>
+        <v>110.6789398193359</v>
       </c>
       <c r="C115" t="n">
         <v>153.5200042724609</v>
@@ -3286,11 +3298,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>127.3110198974609</v>
+        <v>127.3110122680664</v>
       </c>
       <c r="C116" t="n">
         <v>176.5899963378906</v>
@@ -3315,11 +3327,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>109.933479309082</v>
+        <v>109.9335098266602</v>
       </c>
       <c r="C117" t="n">
         <v>151.7799987792969</v>
@@ -3344,7 +3356,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
@@ -3373,11 +3385,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>114.5689468383789</v>
+        <v>114.5689697265625</v>
       </c>
       <c r="C119" t="n">
         <v>158.1799926757812</v>
@@ -3402,7 +3414,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
@@ -3431,11 +3443,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>118.1699600219727</v>
+        <v>118.1699447631836</v>
       </c>
       <c r="C121" t="n">
         <v>162.3300018310547</v>
@@ -3460,7 +3472,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
@@ -3489,11 +3501,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>104.294548034668</v>
+        <v>104.2945251464844</v>
       </c>
       <c r="C123" t="n">
         <v>142.2799987792969</v>
@@ -3518,11 +3530,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>109.9021377563477</v>
+        <v>109.9021606445312</v>
       </c>
       <c r="C124" t="n">
         <v>149.9299926757812</v>
@@ -3547,11 +3559,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>116.0375747680664</v>
+        <v>116.0375442504883</v>
       </c>
       <c r="C125" t="n">
         <v>158.3000030517578</v>
@@ -3576,11 +3588,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>116.5432052612305</v>
+        <v>116.5432281494141</v>
       </c>
       <c r="C126" t="n">
         <v>157.9499969482422</v>
@@ -3605,11 +3617,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>112.2637176513672</v>
+        <v>112.2636947631836</v>
       </c>
       <c r="C127" t="n">
         <v>152.1499938964844</v>
@@ -3634,11 +3646,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>126.9321594238281</v>
+        <v>126.9321746826172</v>
       </c>
       <c r="C128" t="n">
         <v>172.0299987792969</v>
@@ -3663,11 +3675,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>126.2080230712891</v>
+        <v>126.2080535888672</v>
       </c>
       <c r="C129" t="n">
         <v>170.0599975585938</v>
@@ -3692,11 +3704,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>123.7960357666016</v>
+        <v>123.7960662841797</v>
       </c>
       <c r="C130" t="n">
         <v>166.8099975585938</v>
@@ -3721,11 +3733,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>104.7602462768555</v>
+        <v>104.7602615356445</v>
       </c>
       <c r="C131" t="n">
         <v>141.1600036621094</v>
@@ -3750,11 +3762,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>107.64208984375</v>
+        <v>107.6421127319336</v>
       </c>
       <c r="C132" t="n">
         <v>144.0700073242188</v>
@@ -3779,11 +3791,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>109.2409973144531</v>
+        <v>109.2409896850586</v>
       </c>
       <c r="C133" t="n">
         <v>146.2100067138672</v>
@@ -3808,11 +3820,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>117.0636672973633</v>
+        <v>117.0636596679688</v>
       </c>
       <c r="C134" t="n">
         <v>156.6799926757812</v>
@@ -3837,11 +3849,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>132.8042907714844</v>
+        <v>132.8043212890625</v>
       </c>
       <c r="C135" t="n">
         <v>176.5299987792969</v>
@@ -3866,11 +3878,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>123.4305648803711</v>
+        <v>123.4305877685547</v>
       </c>
       <c r="C136" t="n">
         <v>164.0700073242188</v>
@@ -3895,11 +3907,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>122.8663635253906</v>
+        <v>122.8663558959961</v>
       </c>
       <c r="C137" t="n">
         <v>163.3200073242188</v>
@@ -3924,11 +3936,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>117.6320419311523</v>
+        <v>117.632080078125</v>
       </c>
       <c r="C138" t="n">
         <v>155.2400054931641</v>
@@ -3953,11 +3965,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>130.5060882568359</v>
+        <v>130.5060729980469</v>
       </c>
       <c r="C139" t="n">
         <v>172.2299957275391</v>
@@ -3982,7 +3994,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
@@ -4011,11 +4023,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>135.6124572753906</v>
+        <v>135.6125030517578</v>
       </c>
       <c r="C141" t="n">
         <v>177.7700042724609</v>
@@ -4040,11 +4052,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>142.2340393066406</v>
+        <v>142.2340087890625</v>
       </c>
       <c r="C142" t="n">
         <v>186.4499969482422</v>
@@ -4069,11 +4081,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>133.6672058105469</v>
+        <v>133.6671905517578</v>
       </c>
       <c r="C143" t="n">
         <v>175.2200012207031</v>
@@ -4098,7 +4110,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
@@ -4127,7 +4139,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
@@ -4156,11 +4168,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>142.8990478515625</v>
+        <v>142.8991241455078</v>
       </c>
       <c r="C146" t="n">
         <v>186.0500030517578</v>
@@ -4185,11 +4197,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>142.2148742675781</v>
+        <v>142.2148590087891</v>
       </c>
       <c r="C147" t="n">
         <v>183.7700042724609</v>
@@ -4214,11 +4226,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>131.9300384521484</v>
+        <v>131.9300537109375</v>
       </c>
       <c r="C148" t="n">
         <v>170.4799957275391</v>
@@ -4243,11 +4255,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>135.0256042480469</v>
+        <v>135.025634765625</v>
       </c>
       <c r="C149" t="n">
         <v>174.4799957275391</v>
@@ -4272,7 +4284,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
@@ -4301,11 +4313,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>143.9520263671875</v>
+        <v>143.9520416259766</v>
       </c>
       <c r="C151" t="n">
         <v>184.5899963378906</v>
@@ -4330,11 +4342,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>153.2789611816406</v>
+        <v>153.2790222167969</v>
       </c>
       <c r="C152" t="n">
         <v>196.5500030517578</v>
@@ -4359,7 +4371,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
@@ -4388,11 +4400,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>162.7547607421875</v>
+        <v>162.7548217773438</v>
       </c>
       <c r="C154" t="n">
         <v>207.2899932861328</v>
@@ -4417,11 +4429,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>151.3700256347656</v>
+        <v>151.3700866699219</v>
       </c>
       <c r="C155" t="n">
         <v>192.7899932861328</v>
@@ -4446,7 +4458,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
@@ -4475,11 +4487,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>153.9134216308594</v>
+        <v>153.9134521484375</v>
       </c>
       <c r="C157" t="n">
         <v>194.6699981689453</v>
@@ -4504,11 +4516,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>147.9362182617188</v>
+        <v>147.9361724853516</v>
       </c>
       <c r="C158" t="n">
         <v>187.1100006103516</v>
@@ -4533,11 +4545,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>151.4463958740234</v>
+        <v>151.4464263916016</v>
       </c>
       <c r="C159" t="n">
         <v>190.0800018310547</v>
@@ -4562,11 +4574,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>151.3667755126953</v>
+        <v>151.3667144775391</v>
       </c>
       <c r="C160" t="n">
         <v>189.9799957275391</v>
@@ -4591,11 +4603,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>142.8733978271484</v>
+        <v>142.8734130859375</v>
       </c>
       <c r="C161" t="n">
         <v>179.3200073242188</v>
@@ -4620,11 +4632,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>133.9618682861328</v>
+        <v>133.9618530273438</v>
       </c>
       <c r="C162" t="n">
         <v>166.6999969482422</v>
@@ -4649,7 +4661,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
@@ -4678,7 +4690,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
@@ -4707,7 +4719,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
@@ -4736,11 +4748,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>156.6083679199219</v>
+        <v>156.6083221435547</v>
       </c>
       <c r="C166" t="n">
         <v>193.5099945068359</v>
@@ -4765,11 +4777,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>172.5840148925781</v>
+        <v>172.583984375</v>
       </c>
       <c r="C167" t="n">
         <v>213.25</v>
@@ -4794,11 +4806,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>191.2219848632812</v>
+        <v>191.2219390869141</v>
       </c>
       <c r="C168" t="n">
         <v>234.7200012207031</v>
@@ -4823,7 +4835,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
@@ -4852,11 +4864,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>176.0118713378906</v>
+        <v>176.0118865966797</v>
       </c>
       <c r="C170" t="n">
         <v>216.0500030517578</v>
@@ -4881,7 +4893,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
@@ -4910,11 +4922,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>166.3326873779297</v>
+        <v>166.3327484130859</v>
       </c>
       <c r="C172" t="n">
         <v>202.7299957275391</v>
@@ -4939,7 +4951,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
@@ -4968,11 +4980,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>189.7362976074219</v>
+        <v>189.7362670898438</v>
       </c>
       <c r="C174" t="n">
         <v>229.6999969482422</v>
@@ -4997,7 +5009,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
@@ -5026,11 +5038,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>202.1017456054688</v>
+        <v>202.1017913818359</v>
       </c>
       <c r="C176" t="n">
         <v>244.6699981689453</v>
@@ -5055,11 +5067,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>210.6484680175781</v>
+        <v>210.6484527587891</v>
       </c>
       <c r="C177" t="n">
         <v>253.3200073242188</v>
@@ -5084,11 +5096,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>211.3469696044922</v>
+        <v>211.3469543457031</v>
       </c>
       <c r="C178" t="n">
         <v>254.1600036621094</v>
@@ -5113,11 +5125,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>180.3966674804688</v>
+        <v>180.3966217041016</v>
       </c>
       <c r="C179" t="n">
         <v>216.9400024414062</v>
@@ -5142,7 +5154,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
@@ -5171,11 +5183,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>192.4888916015625</v>
+        <v>192.4889068603516</v>
       </c>
       <c r="C181" t="n">
         <v>229.9199981689453</v>
@@ -5200,11 +5212,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>202.1250610351562</v>
+        <v>202.1250457763672</v>
       </c>
       <c r="C182" t="n">
         <v>241.4299926757812</v>
@@ -5229,11 +5241,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>189.7030181884766</v>
+        <v>189.7030334472656</v>
       </c>
       <c r="C183" t="n">
         <v>224.9199981689453</v>
@@ -5258,11 +5270,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>209.8524169921875</v>
+        <v>209.8524475097656</v>
       </c>
       <c r="C184" t="n">
         <v>248.8099975585938</v>
@@ -5287,11 +5299,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>202.1182708740234</v>
+        <v>202.1181945800781</v>
       </c>
       <c r="C185" t="n">
         <v>239.6399993896484</v>
@@ -5316,11 +5328,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>202.0955352783203</v>
+        <v>202.0955047607422</v>
       </c>
       <c r="C186" t="n">
         <v>237.9400024414062</v>
@@ -5345,11 +5357,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>207.0302429199219</v>
+        <v>207.0302734375</v>
       </c>
       <c r="C187" t="n">
         <v>243.75</v>
@@ -5374,11 +5386,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>205.1531677246094</v>
+        <v>205.1531524658203</v>
       </c>
       <c r="C188" t="n">
         <v>241.5399932861328</v>
@@ -5403,11 +5415,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>193.0341796875</v>
+        <v>193.0342254638672</v>
       </c>
       <c r="C189" t="n">
         <v>225.5299987792969</v>
@@ -5432,11 +5444,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>182.0100250244141</v>
+        <v>182.010009765625</v>
       </c>
       <c r="C190" t="n">
         <v>212.6499938964844</v>
@@ -5461,7 +5473,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
@@ -5490,11 +5502,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>171.6532745361328</v>
+        <v>171.6532440185547</v>
       </c>
       <c r="C192" t="n">
         <v>198.8800048828125</v>
@@ -5519,11 +5531,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>194.1715240478516</v>
+        <v>194.1715087890625</v>
       </c>
       <c r="C193" t="n">
         <v>224.9700012207031</v>
@@ -5548,11 +5560,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>196.0444183349609</v>
+        <v>196.0444488525391</v>
       </c>
       <c r="C194" t="n">
         <v>227.1399993896484</v>
@@ -5577,11 +5589,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>197.1508178710938</v>
+        <v>197.1508331298828</v>
       </c>
       <c r="C195" t="n">
         <v>226.4799957275391</v>
@@ -5606,11 +5618,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>210.5043029785156</v>
+        <v>210.5043334960938</v>
       </c>
       <c r="C196" t="n">
         <v>241.8200073242188</v>
@@ -5635,11 +5647,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>202.9918975830078</v>
+        <v>202.9918823242188</v>
       </c>
       <c r="C197" t="n">
         <v>233.1900024414062</v>
@@ -5664,11 +5676,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>225.2877502441406</v>
+        <v>225.2877960205078</v>
       </c>
       <c r="C198" t="n">
         <v>256.739990234375</v>
@@ -5693,7 +5705,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
@@ -5722,11 +5734,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>217.1534423828125</v>
+        <v>217.1533966064453</v>
       </c>
       <c r="C200" t="n">
         <v>247.4700012207031</v>
@@ -5751,11 +5763,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>212.4902191162109</v>
+        <v>212.4902038574219</v>
       </c>
       <c r="C201" t="n">
         <v>240.3000030517578</v>
@@ -5780,11 +5792,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>199.3146057128906</v>
+        <v>199.3145599365234</v>
       </c>
       <c r="C202" t="n">
         <v>225.3999938964844</v>
@@ -5809,11 +5821,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>239.0625457763672</v>
+        <v>239.0625152587891</v>
       </c>
       <c r="C203" t="n">
         <v>270.3500061035156</v>
@@ -5838,7 +5850,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
@@ -5867,11 +5879,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>233.8444366455078</v>
+        <v>233.8444671630859</v>
       </c>
       <c r="C205" t="n">
         <v>262.6400146484375</v>
@@ -5896,11 +5908,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>224.7271575927734</v>
+        <v>224.7271423339844</v>
       </c>
       <c r="C206" t="n">
         <v>252.3999938964844</v>
@@ -5925,11 +5937,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>208.0800323486328</v>
+        <v>208.0800476074219</v>
       </c>
       <c r="C207" t="n">
         <v>231.6600036621094</v>
@@ -5954,7 +5966,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
@@ -5983,7 +5995,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
@@ -6012,11 +6024,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>200.0606842041016</v>
+        <v>200.0606536865234</v>
       </c>
       <c r="C210" t="n">
         <v>220.6499938964844</v>
@@ -6041,11 +6053,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>201.3028411865234</v>
+        <v>201.3028259277344</v>
       </c>
       <c r="C211" t="n">
         <v>222.0200042724609</v>
@@ -6070,7 +6082,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
@@ -6099,11 +6111,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>234.3035125732422</v>
+        <v>234.3034820556641</v>
       </c>
       <c r="C213" t="n">
         <v>256.3399963378906</v>
@@ -6128,11 +6140,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>245.6558532714844</v>
+        <v>245.6557922363281</v>
       </c>
       <c r="C214" t="n">
         <v>268.760009765625</v>
@@ -6157,7 +6169,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
@@ -6186,11 +6198,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>248.3979797363281</v>
+        <v>248.3979949951172</v>
       </c>
       <c r="C216" t="n">
         <v>269.6400146484375</v>
@@ -6215,7 +6227,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
@@ -6244,11 +6256,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>289.5028991699219</v>
+        <v>289.5028381347656</v>
       </c>
       <c r="C218" t="n">
         <v>314.260009765625</v>
@@ -6273,11 +6285,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>254.2298431396484</v>
+        <v>254.2299041748047</v>
       </c>
       <c r="C219" t="n">
         <v>273.8299865722656</v>
@@ -6302,11 +6314,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>263.9690551757812</v>
+        <v>263.9691162109375</v>
       </c>
       <c r="C220" t="n">
         <v>284.3200073242188</v>
@@ -6331,11 +6343,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>254.33203125</v>
+        <v>254.3320465087891</v>
       </c>
       <c r="C221" t="n">
         <v>273.9400024414062</v>
@@ -6360,7 +6372,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
@@ -6389,11 +6401,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>292.1459045410156</v>
+        <v>292.14599609375</v>
       </c>
       <c r="C223" t="n">
         <v>312.4500122070312</v>
@@ -6418,11 +6430,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>310.864990234375</v>
+        <v>310.8649597167969</v>
       </c>
       <c r="C224" t="n">
         <v>332.4700012207031</v>
@@ -6447,11 +6459,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>314.3099670410156</v>
+        <v>314.3099365234375</v>
       </c>
       <c r="C225" t="n">
         <v>333.8299865722656</v>
@@ -6476,11 +6488,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>303.3693542480469</v>
+        <v>303.3694152832031</v>
       </c>
       <c r="C226" t="n">
         <v>322.2099914550781</v>
@@ -6505,11 +6517,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>301.4393005371094</v>
+        <v>301.4392700195312</v>
       </c>
       <c r="C227" t="n">
         <v>320.1600036621094</v>
@@ -6534,11 +6546,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>268.4595642089844</v>
+        <v>268.4595336914062</v>
       </c>
       <c r="C228" t="n">
         <v>282.8699951171875</v>
@@ -6563,11 +6575,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>247.362060546875</v>
+        <v>247.3620452880859</v>
       </c>
       <c r="C229" t="n">
         <v>260.6400146484375</v>
@@ -6592,7 +6604,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
@@ -6621,11 +6633,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>294.7283325195312</v>
+        <v>294.7283020019531</v>
       </c>
       <c r="C231" t="n">
         <v>308.0599975585938</v>
@@ -6650,11 +6662,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>298.0672912597656</v>
+        <v>298.0672302246094</v>
       </c>
       <c r="C232" t="n">
         <v>311.5499877929688</v>
@@ -6679,7 +6691,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -6708,7 +6720,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
@@ -6737,11 +6749,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>269.4875183105469</v>
+        <v>269.487548828125</v>
       </c>
       <c r="C235" t="n">
         <v>279.2099914550781</v>
@@ -6766,7 +6778,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6795,11 +6807,11 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>279.9443054199219</v>
+        <v>279.9442443847656</v>
       </c>
       <c r="C237" t="n">
         <v>287.7099914550781</v>
@@ -6824,11 +6836,11 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>274.5830078125</v>
+        <v>274.5830383300781</v>
       </c>
       <c r="C238" t="n">
         <v>282.2000122070312</v>
@@ -6853,11 +6865,11 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>290.3749084472656</v>
+        <v>290.3749389648438</v>
       </c>
       <c r="C239" t="n">
         <v>298.4299926757812</v>
@@ -6882,11 +6894,11 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>338.5329284667969</v>
+        <v>338.5329895019531</v>
       </c>
       <c r="C240" t="n">
         <v>345.4599914550781</v>
@@ -6911,7 +6923,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6940,7 +6952,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6969,7 +6981,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6998,7 +7010,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7027,7 +7039,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7056,7 +7068,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7085,7 +7097,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7114,7 +7126,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7143,7 +7155,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7172,32 +7184,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>406.0899963378906</v>
+        <v>406.0400085449219</v>
       </c>
       <c r="C250" t="n">
-        <v>406.0899963378906</v>
+        <v>406.0400085449219</v>
       </c>
       <c r="D250" t="n">
-        <v>52499600</v>
+        <v>55024600</v>
       </c>
       <c r="E250" t="n">
         <v>16.09</v>
       </c>
       <c r="F250" t="n">
-        <v>25.2386573236725</v>
+        <v>25.23555056214554</v>
       </c>
       <c r="G250" t="n">
         <v>540632005</v>
       </c>
       <c r="H250" t="n">
-        <v>219545248930.5965</v>
+        <v>219518223929.8582</v>
       </c>
       <c r="I250" t="n">
-        <v>0.09710782845717764</v>
+        <v>0.1017782881721921</v>
       </c>
     </row>
   </sheetData>
@@ -7229,75 +7241,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40035</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7333,13 +7345,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7375,13 +7387,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7417,13 +7429,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40035</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7459,13 +7471,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7501,13 +7513,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7534,7 +7546,7 @@
       <c r="I7" t="n">
         <v>4.51</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K7" t="n">
@@ -7547,13 +7559,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7580,7 +7592,7 @@
       <c r="I8" t="n">
         <v>4.71</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K8" t="n">
@@ -7593,13 +7605,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40399</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7626,7 +7638,7 @@
       <c r="I9" t="n">
         <v>4.71</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K9" t="n">
@@ -7639,13 +7651,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40490</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7672,7 +7684,7 @@
       <c r="I10" t="n">
         <v>4.63</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K10" t="n">
@@ -7685,13 +7697,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7718,7 +7730,7 @@
       <c r="I11" t="n">
         <v>4.79</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K11" t="n">
@@ -7731,13 +7743,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40673</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7764,7 +7776,7 @@
       <c r="I12" t="n">
         <v>4.81</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40673</v>
       </c>
       <c r="K12" t="n">
@@ -7777,13 +7789,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40763</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7810,7 +7822,7 @@
       <c r="I13" t="n">
         <v>4.81</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40763</v>
       </c>
       <c r="K13" t="n">
@@ -7823,13 +7835,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40851</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7856,7 +7868,7 @@
       <c r="I14" t="n">
         <v>4.029999999999999</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40851</v>
       </c>
       <c r="K14" t="n">
@@ -7869,13 +7881,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7902,7 +7914,7 @@
       <c r="I15" t="n">
         <v>4.029999999999999</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="K15" t="n">
@@ -7915,13 +7927,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41037</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7948,7 +7960,7 @@
       <c r="I16" t="n">
         <v>4.31</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41037</v>
       </c>
       <c r="K16" t="n">
@@ -7961,13 +7973,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41129</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7994,7 +8006,7 @@
       <c r="I17" t="n">
         <v>4.67</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41129</v>
       </c>
       <c r="K17" t="n">
@@ -8007,13 +8019,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41219</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8040,7 +8052,7 @@
       <c r="I18" t="n">
         <v>5.58</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41219</v>
       </c>
       <c r="K18" t="n">
@@ -8053,13 +8065,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41332</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8086,7 +8098,7 @@
       <c r="I19" t="n">
         <v>5.51</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41332</v>
       </c>
       <c r="K19" t="n">
@@ -8099,13 +8111,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41397</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8132,7 +8144,7 @@
       <c r="I20" t="n">
         <v>5.909999999999999</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41397</v>
       </c>
       <c r="K20" t="n">
@@ -8145,13 +8157,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41492</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8178,7 +8190,7 @@
       <c r="I21" t="n">
         <v>5.95</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41492</v>
       </c>
       <c r="K21" t="n">
@@ -8191,13 +8203,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41576</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8224,7 +8236,7 @@
       <c r="I22" t="n">
         <v>6.33</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41576</v>
       </c>
       <c r="K22" t="n">
@@ -8237,13 +8249,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41694</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8270,7 +8282,7 @@
       <c r="I23" t="n">
         <v>6.65</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41694</v>
       </c>
       <c r="K23" t="n">
@@ -8283,13 +8295,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8316,7 +8328,7 @@
       <c r="I24" t="n">
         <v>6.17</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="K24" t="n">
@@ -8329,13 +8341,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41856</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8362,7 +8374,7 @@
       <c r="I25" t="n">
         <v>6.529999999999999</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41856</v>
       </c>
       <c r="K25" t="n">
@@ -8375,13 +8387,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41941</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8408,7 +8420,7 @@
       <c r="I26" t="n">
         <v>6.35</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41941</v>
       </c>
       <c r="K26" t="n">
@@ -8421,13 +8433,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42054</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8454,7 +8466,7 @@
       <c r="I27" t="n">
         <v>6.699999999999999</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42054</v>
       </c>
       <c r="K27" t="n">
@@ -8467,13 +8479,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42121</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8500,7 +8512,7 @@
       <c r="I28" t="n">
         <v>7.41</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42121</v>
       </c>
       <c r="K28" t="n">
@@ -8513,13 +8525,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42221</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8546,7 +8558,7 @@
       <c r="I29" t="n">
         <v>7.55</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42221</v>
       </c>
       <c r="K29" t="n">
@@ -8559,13 +8571,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42310</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8592,7 +8604,7 @@
       <c r="I30" t="n">
         <v>8.379999999999999</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42310</v>
       </c>
       <c r="K30" t="n">
@@ -8605,13 +8617,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42416</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8638,7 +8650,7 @@
       <c r="I31" t="n">
         <v>9.07</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42416</v>
       </c>
       <c r="K31" t="n">
@@ -8651,13 +8663,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42492</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8684,7 +8696,7 @@
       <c r="I32" t="n">
         <v>9.460000000000001</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42492</v>
       </c>
       <c r="K32" t="n">
@@ -8697,13 +8709,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42580</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8730,7 +8742,7 @@
       <c r="I33" t="n">
         <v>9.780000000000001</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42580</v>
       </c>
       <c r="K33" t="n">
@@ -8743,13 +8755,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42671</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8776,7 +8788,7 @@
       <c r="I34" t="n">
         <v>10.02</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42671</v>
       </c>
       <c r="K34" t="n">
@@ -8789,13 +8801,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42780</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8822,7 +8834,7 @@
       <c r="I35" t="n">
         <v>10.24</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42780</v>
       </c>
       <c r="K35" t="n">
@@ -8835,13 +8847,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42852</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8868,7 +8880,7 @@
       <c r="I36" t="n">
         <v>10.53</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42852</v>
       </c>
       <c r="K36" t="n">
@@ -8881,13 +8893,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42942</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8914,7 +8926,7 @@
       <c r="I37" t="n">
         <v>10.97</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42942</v>
       </c>
       <c r="K37" t="n">
@@ -8927,13 +8939,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43034</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8960,7 +8972,7 @@
       <c r="I38" t="n">
         <v>11.05</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43034</v>
       </c>
       <c r="K38" t="n">
@@ -8973,13 +8985,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43144</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -9006,7 +9018,7 @@
       <c r="I39" t="n">
         <v>2.57</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43144</v>
       </c>
       <c r="K39" t="n">
@@ -9019,13 +9031,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43215</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9052,7 +9064,7 @@
       <c r="I40" t="n">
         <v>3.030000000000001</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43215</v>
       </c>
       <c r="K40" t="n">
@@ -9065,13 +9077,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43308</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9098,7 +9110,7 @@
       <c r="I41" t="n">
         <v>3.600000000000001</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43308</v>
       </c>
       <c r="K41" t="n">
@@ -9111,13 +9123,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9144,7 +9156,7 @@
       <c r="I42" t="n">
         <v>3.700000000000001</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="K42" t="n">
@@ -9157,13 +9169,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43509</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9190,7 +9202,7 @@
       <c r="I43" t="n">
         <v>12.6</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43509</v>
       </c>
       <c r="K43" t="n">
@@ -9203,13 +9215,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9236,7 +9248,7 @@
       <c r="I44" t="n">
         <v>12.53</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="K44" t="n">
@@ -9249,13 +9261,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9282,7 +9294,7 @@
       <c r="I45" t="n">
         <v>12.62</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="K45" t="n">
@@ -9295,13 +9307,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43768</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9328,7 +9340,7 @@
       <c r="I46" t="n">
         <v>13.03</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43768</v>
       </c>
       <c r="K46" t="n">
@@ -9341,13 +9353,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43873</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9374,7 +9386,7 @@
       <c r="I47" t="n">
         <v>12.87</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43873</v>
       </c>
       <c r="K47" t="n">
@@ -9387,13 +9399,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9420,7 +9432,7 @@
       <c r="I48" t="n">
         <v>12.76</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="K48" t="n">
@@ -9433,13 +9445,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44041</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9466,7 +9478,7 @@
       <c r="I49" t="n">
         <v>12.24</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44041</v>
       </c>
       <c r="K49" t="n">
@@ -9479,13 +9491,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44133</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9512,7 +9524,7 @@
       <c r="I50" t="n">
         <v>12.4</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44133</v>
       </c>
       <c r="K50" t="n">
@@ -9525,13 +9537,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44236</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9558,7 +9570,7 @@
       <c r="I51" t="n">
         <v>12.31</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44236</v>
       </c>
       <c r="K51" t="n">
@@ -9571,13 +9583,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44314</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9604,7 +9616,7 @@
       <c r="I52" t="n">
         <v>12.07</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44314</v>
       </c>
       <c r="K52" t="n">
@@ -9617,13 +9629,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44412</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9650,7 +9662,7 @@
       <c r="I53" t="n">
         <v>9.830000000000002</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44412</v>
       </c>
       <c r="K53" t="n">
@@ -9663,13 +9675,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44503</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9696,7 +9708,7 @@
       <c r="I54" t="n">
         <v>9.710000000000001</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44503</v>
       </c>
       <c r="K54" t="n">
@@ -9709,13 +9721,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44608</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9742,7 +9754,7 @@
       <c r="I55" t="n">
         <v>10.28</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44608</v>
       </c>
       <c r="K55" t="n">
@@ -9755,13 +9767,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44679</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9788,7 +9800,7 @@
       <c r="I56" t="n">
         <v>10.13</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44679</v>
       </c>
       <c r="K56" t="n">
@@ -9801,13 +9813,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44778</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9834,7 +9846,7 @@
       <c r="I57" t="n">
         <v>11.77</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44778</v>
       </c>
       <c r="K57" t="n">
@@ -9847,13 +9859,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44869</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9880,7 +9892,7 @@
       <c r="I58" t="n">
         <v>12.44</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44869</v>
       </c>
       <c r="K58" t="n">
@@ -9893,13 +9905,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44966</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9926,7 +9938,7 @@
       <c r="I59" t="n">
         <v>12.11</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44966</v>
       </c>
       <c r="K59" t="n">
@@ -9939,13 +9951,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45044</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9972,7 +9984,7 @@
       <c r="I60" t="n">
         <v>14.71</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45044</v>
       </c>
       <c r="K60" t="n">
@@ -9985,13 +9997,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45142</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -10018,7 +10030,7 @@
       <c r="I61" t="n">
         <v>14.83</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45142</v>
       </c>
       <c r="K61" t="n">
@@ -10031,13 +10043,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10064,7 +10076,7 @@
       <c r="I62" t="n">
         <v>14.07</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="K62" t="n">
@@ -10077,13 +10089,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45336</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10110,7 +10122,7 @@
       <c r="I63" t="n">
         <v>12.49</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45336</v>
       </c>
       <c r="K63" t="n">
@@ -10123,13 +10135,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45415</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10156,7 +10168,7 @@
       <c r="I64" t="n">
         <v>7.000000000000001</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45415</v>
       </c>
       <c r="K64" t="n">
@@ -10169,13 +10181,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45511</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10202,7 +10214,7 @@
       <c r="I65" t="n">
         <v>5.810000000000001</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45511</v>
       </c>
       <c r="K65" t="n">
@@ -10215,13 +10227,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10248,7 +10260,7 @@
       <c r="I66" t="n">
         <v>7.81</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="K66" t="n">
@@ -10261,13 +10273,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45702</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10294,7 +10306,7 @@
       <c r="I67" t="n">
         <v>7.56</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45702</v>
       </c>
       <c r="K67" t="n">
@@ -10307,13 +10319,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10340,7 +10352,7 @@
       <c r="I68" t="n">
         <v>10.97</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="K68" t="n">
@@ -10353,13 +10365,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10386,7 +10398,7 @@
       <c r="I69" t="n">
         <v>12.24</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="K69" t="n">
@@ -10399,13 +10411,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45966</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10432,7 +10444,7 @@
       <c r="I70" t="n">
         <v>12.95</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45966</v>
       </c>
       <c r="K70" t="n">
@@ -10445,13 +10457,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46066</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10478,7 +10490,7 @@
       <c r="I71" t="n">
         <v>14.23</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46066</v>
       </c>
       <c r="K71" t="n">
@@ -10491,13 +10503,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10524,7 +10536,7 @@
       <c r="I72" t="n">
         <v>14.37</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="K72" t="n">
@@ -10537,13 +10549,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46239</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10570,7 +10582,7 @@
       <c r="I73" t="n">
         <v>16.09</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46239</v>
       </c>
       <c r="K73" t="n">
@@ -10607,52 +10619,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40028</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40035</v>
       </c>
       <c r="C2" t="n">
@@ -10681,10 +10693,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40119</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="C3" t="n">
@@ -10713,10 +10725,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40221</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40238</v>
       </c>
       <c r="C4" t="n">
@@ -10745,10 +10757,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40301</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="C5" t="n">
@@ -10777,10 +10789,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40389</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40399</v>
       </c>
       <c r="C6" t="n">
@@ -10809,10 +10821,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40480</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40490</v>
       </c>
       <c r="C7" t="n">
@@ -10841,10 +10853,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40585</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="C8" t="n">
@@ -10873,10 +10885,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40662</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40673</v>
       </c>
       <c r="C9" t="n">
@@ -10905,10 +10917,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40751</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40763</v>
       </c>
       <c r="C10" t="n">
@@ -10937,10 +10949,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40842</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40851</v>
       </c>
       <c r="C11" t="n">
@@ -10969,10 +10981,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40949</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="C12" t="n">
@@ -11001,10 +11013,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41025</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41037</v>
       </c>
       <c r="C13" t="n">
@@ -11033,10 +11045,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41115</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41129</v>
       </c>
       <c r="C14" t="n">
@@ -11065,10 +11077,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41211</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41219</v>
       </c>
       <c r="C15" t="n">
@@ -11097,10 +11109,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41324</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41332</v>
       </c>
       <c r="C16" t="n">
@@ -11129,10 +11141,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41388</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41397</v>
       </c>
       <c r="C17" t="n">
@@ -11161,10 +11173,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41485</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41492</v>
       </c>
       <c r="C18" t="n">
@@ -11193,10 +11205,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41569</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41576</v>
       </c>
       <c r="C19" t="n">
@@ -11225,10 +11237,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41683</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41694</v>
       </c>
       <c r="C20" t="n">
@@ -11257,10 +11269,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41751</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="C21" t="n">
@@ -11289,10 +11301,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41849</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41856</v>
       </c>
       <c r="C22" t="n">
@@ -11321,10 +11333,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41933</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41941</v>
       </c>
       <c r="C23" t="n">
@@ -11353,10 +11365,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42047</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42054</v>
       </c>
       <c r="C24" t="n">
@@ -11385,10 +11397,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42114</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42121</v>
       </c>
       <c r="C25" t="n">
@@ -11417,10 +11429,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42213</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42221</v>
       </c>
       <c r="C26" t="n">
@@ -11449,10 +11461,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42304</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42310</v>
       </c>
       <c r="C27" t="n">
@@ -11481,10 +11493,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42409</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42416</v>
       </c>
       <c r="C28" t="n">
@@ -11513,10 +11525,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42485</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42492</v>
       </c>
       <c r="C29" t="n">
@@ -11545,10 +11557,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42576</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42580</v>
       </c>
       <c r="C30" t="n">
@@ -11577,10 +11589,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42667</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42671</v>
       </c>
       <c r="C31" t="n">
@@ -11609,10 +11621,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42775</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42780</v>
       </c>
       <c r="C32" t="n">
@@ -11641,10 +11653,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42843</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42852</v>
       </c>
       <c r="C33" t="n">
@@ -11673,10 +11685,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42934</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42942</v>
       </c>
       <c r="C34" t="n">
@@ -11705,10 +11717,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43025</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43034</v>
       </c>
       <c r="C35" t="n">
@@ -11737,10 +11749,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43140</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43144</v>
       </c>
       <c r="C36" t="n">
@@ -11769,10 +11781,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43208</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43215</v>
       </c>
       <c r="C37" t="n">
@@ -11801,10 +11813,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43299</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43308</v>
       </c>
       <c r="C38" t="n">
@@ -11833,10 +11845,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43397</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="C39" t="n">
@@ -11865,10 +11877,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43503</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43509</v>
       </c>
       <c r="C40" t="n">
@@ -11897,10 +11909,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43579</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="C41" t="n">
@@ -11929,10 +11941,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43670</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="C42" t="n">
@@ -11961,10 +11973,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43761</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43768</v>
       </c>
       <c r="C43" t="n">
@@ -11993,10 +12005,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43867</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43873</v>
       </c>
       <c r="C44" t="n">
@@ -12025,10 +12037,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43948</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="C45" t="n">
@@ -12057,10 +12069,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44035</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44041</v>
       </c>
       <c r="C46" t="n">
@@ -12089,10 +12101,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44127</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44133</v>
       </c>
       <c r="C47" t="n">
@@ -12121,10 +12133,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44230</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44236</v>
       </c>
       <c r="C48" t="n">
@@ -12153,10 +12165,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44308</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44314</v>
       </c>
       <c r="C49" t="n">
@@ -12185,10 +12197,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44406</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44412</v>
       </c>
       <c r="C50" t="n">
@@ -12217,10 +12229,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44497</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44503</v>
       </c>
       <c r="C51" t="n">
@@ -12249,10 +12261,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44603</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44608</v>
       </c>
       <c r="C52" t="n">
@@ -12281,10 +12293,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44673</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44679</v>
       </c>
       <c r="C53" t="n">
@@ -12313,10 +12325,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44774</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44778</v>
       </c>
       <c r="C54" t="n">
@@ -12345,10 +12357,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44865</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44869</v>
       </c>
       <c r="C55" t="n">
@@ -12377,10 +12389,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44963</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44966</v>
       </c>
       <c r="C56" t="n">
@@ -12409,10 +12421,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45040</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45044</v>
       </c>
       <c r="C57" t="n">
@@ -12441,10 +12453,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45138</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45142</v>
       </c>
       <c r="C58" t="n">
@@ -12473,10 +12485,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45225</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="C59" t="n">
@@ -12505,10 +12517,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45331</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45336</v>
       </c>
       <c r="C60" t="n">
@@ -12537,10 +12549,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45411</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45415</v>
       </c>
       <c r="C61" t="n">
@@ -12569,10 +12581,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45505</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45511</v>
       </c>
       <c r="C62" t="n">
@@ -12601,10 +12613,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45590</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="C63" t="n">
@@ -12633,10 +12645,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45699</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45702</v>
       </c>
       <c r="C64" t="n">
@@ -12665,10 +12677,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45775</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="C65" t="n">
@@ -12697,10 +12709,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45869</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="C66" t="n">
@@ -12729,10 +12741,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45960</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45966</v>
       </c>
       <c r="C67" t="n">
@@ -12761,10 +12773,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46063</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46066</v>
       </c>
       <c r="C68" t="n">
@@ -12793,10 +12805,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46139</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="C69" t="n">
@@ -12825,10 +12837,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46233</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46239</v>
       </c>
       <c r="C70" t="n">
@@ -12875,12 +12887,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/AMGN.xlsx
+++ b/salidas/empresas/AMGN.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>48.64816284179688</v>
+        <v>48.64815521240234</v>
       </c>
       <c r="C2" t="n">
         <v>72.88999938964844</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>50.37677383422852</v>
+        <v>50.37677001953125</v>
       </c>
       <c r="C3" t="n">
         <v>75.48000335693359</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>48.55471801757812</v>
+        <v>48.55474472045898</v>
       </c>
       <c r="C4" t="n">
         <v>72.75</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>45.18425369262695</v>
+        <v>45.18424606323242</v>
       </c>
       <c r="C5" t="n">
         <v>67.69999694824219</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>45.11083984375</v>
+        <v>45.11085891723633</v>
       </c>
       <c r="C6" t="n">
         <v>67.58999633789062</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>43.53573226928711</v>
+        <v>43.53572845458984</v>
       </c>
       <c r="C7" t="n">
         <v>65.23000335693359</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>46.52575302124023</v>
+        <v>46.52577209472656</v>
       </c>
       <c r="C8" t="n">
         <v>69.70999908447266</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>45.40450668334961</v>
+        <v>45.40451812744141</v>
       </c>
       <c r="C9" t="n">
         <v>68.02999877929688</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>47.74046325683594</v>
+        <v>47.74045944213867</v>
       </c>
       <c r="C10" t="n">
         <v>71.52999877929688</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>50.66376495361328</v>
+        <v>50.66376876831055</v>
       </c>
       <c r="C11" t="n">
         <v>75.91000366210938</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>47.41344451904297</v>
+        <v>47.4134407043457</v>
       </c>
       <c r="C12" t="n">
         <v>71.04000091552734</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>45.59138107299805</v>
+        <v>45.59138488769531</v>
       </c>
       <c r="C13" t="n">
         <v>68.30999755859375</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>46.96626281738281</v>
+        <v>46.96627044677734</v>
       </c>
       <c r="C14" t="n">
         <v>70.37000274658203</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>42.88833618164062</v>
+        <v>42.88833999633789</v>
       </c>
       <c r="C15" t="n">
         <v>64.26000213623047</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>42.8082389831543</v>
+        <v>42.80825424194336</v>
       </c>
       <c r="C17" t="n">
         <v>64.13999938964844</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>37.67579650878906</v>
+        <v>37.67578506469727</v>
       </c>
       <c r="C18" t="n">
         <v>56.45000076293945</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>36.90158081054688</v>
+        <v>36.90159606933594</v>
       </c>
       <c r="C19" t="n">
         <v>55.29000091552734</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>35.86708450317383</v>
+        <v>35.86708068847656</v>
       </c>
       <c r="C20" t="n">
         <v>53.7400016784668</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>37.75588607788086</v>
+        <v>37.75588226318359</v>
       </c>
       <c r="C22" t="n">
         <v>56.56999969482422</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>38.7837028503418</v>
+        <v>38.78371429443359</v>
       </c>
       <c r="C23" t="n">
         <v>58.11000061035156</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>36.87489700317383</v>
+        <v>36.87490844726562</v>
       </c>
       <c r="C24" t="n">
         <v>55.25</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>30.99492263793945</v>
+        <v>30.99493408203125</v>
       </c>
       <c r="C25" t="n">
         <v>46.43999862670898</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>31.09504318237305</v>
+        <v>31.09504127502441</v>
       </c>
       <c r="C26" t="n">
         <v>46.59000015258789</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>30.38089752197266</v>
+        <v>30.38090324401855</v>
       </c>
       <c r="C27" t="n">
         <v>45.52000045776367</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>27.88474464416504</v>
+        <v>27.88476181030273</v>
       </c>
       <c r="C28" t="n">
         <v>41.77999877929688</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>27.94482612609863</v>
+        <v>27.94482803344727</v>
       </c>
       <c r="C29" t="n">
         <v>41.86999893188477</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>29.38646125793457</v>
+        <v>29.38645172119141</v>
       </c>
       <c r="C30" t="n">
         <v>44.02999877929688</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>31.47546195983887</v>
+        <v>31.4754753112793</v>
       </c>
       <c r="C31" t="n">
         <v>47.15999984741211</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>41.80045318603516</v>
+        <v>41.80044555664062</v>
       </c>
       <c r="C32" t="n">
         <v>62.63000106811523</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>39.55790710449219</v>
+        <v>39.55790328979492</v>
       </c>
       <c r="C34" t="n">
         <v>59.27000045776367</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>39.97171020507812</v>
+        <v>39.97172164916992</v>
       </c>
       <c r="C35" t="n">
         <v>59.88999938964844</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>38.54343032836914</v>
+        <v>38.5434455871582</v>
       </c>
       <c r="C37" t="n">
         <v>57.75</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>36.60792922973633</v>
+        <v>36.6079216003418</v>
       </c>
       <c r="C38" t="n">
         <v>54.84999847412109</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>32.65680694580078</v>
+        <v>32.65681076049805</v>
       </c>
       <c r="C39" t="n">
         <v>48.93000030517578</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>33.05058670043945</v>
+        <v>33.05058288574219</v>
       </c>
       <c r="C40" t="n">
         <v>49.52000045776367</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>32.34979629516602</v>
+        <v>32.34979248046875</v>
       </c>
       <c r="C41" t="n">
         <v>48.47000122070312</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>33.33090209960938</v>
+        <v>33.33089065551758</v>
       </c>
       <c r="C42" t="n">
         <v>49.93999862670898</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>41.58686447143555</v>
+        <v>41.58687591552734</v>
       </c>
       <c r="C44" t="n">
         <v>62.31000137329102</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>39.89829254150391</v>
+        <v>39.89829635620117</v>
       </c>
       <c r="C45" t="n">
         <v>59.77999877929688</v>
@@ -1340,7 +1340,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>40.19863891601562</v>
+        <v>40.19863128662109</v>
       </c>
       <c r="C46" t="n">
         <v>60.22999954223633</v>
@@ -1365,7 +1365,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>35.78700256347656</v>
+        <v>35.78700637817383</v>
       </c>
       <c r="C47" t="n">
         <v>53.61999893188477</v>
@@ -1390,7 +1390,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>37.60905075073242</v>
+        <v>37.60905456542969</v>
       </c>
       <c r="C48" t="n">
         <v>56.34999847412109</v>
@@ -1415,7 +1415,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>37.75588607788086</v>
+        <v>37.75588226318359</v>
       </c>
       <c r="C49" t="n">
         <v>56.56999969482422</v>
@@ -1440,7 +1440,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>39.0306510925293</v>
+        <v>39.03064727783203</v>
       </c>
       <c r="C50" t="n">
         <v>58.47999954223633</v>
@@ -1465,7 +1465,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>37.78258514404297</v>
+        <v>37.78257369995117</v>
       </c>
       <c r="C51" t="n">
         <v>56.61000061035156</v>
@@ -1490,7 +1490,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>39.9383430480957</v>
+        <v>39.93833160400391</v>
       </c>
       <c r="C52" t="n">
         <v>59.84000015258789</v>
@@ -1515,7 +1515,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>38.24978256225586</v>
+        <v>38.24977874755859</v>
       </c>
       <c r="C53" t="n">
         <v>57.31000137329102</v>
@@ -1540,7 +1540,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>34.55895233154297</v>
+        <v>34.55894470214844</v>
       </c>
       <c r="C54" t="n">
         <v>51.77999877929688</v>
@@ -1565,7 +1565,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>35.10624694824219</v>
+        <v>35.10622787475586</v>
       </c>
       <c r="C55" t="n">
         <v>52.59999847412109</v>
@@ -1590,7 +1590,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>36.39434814453125</v>
+        <v>36.39435195922852</v>
       </c>
       <c r="C56" t="n">
         <v>54.52999877929688</v>
@@ -1615,7 +1615,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>34.06506729125977</v>
+        <v>34.06505966186523</v>
       </c>
       <c r="C57" t="n">
         <v>51.04000091552734</v>
@@ -1640,7 +1640,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>36.78145980834961</v>
+        <v>36.78144836425781</v>
       </c>
       <c r="C58" t="n">
         <v>55.11000061035156</v>
@@ -1665,7 +1665,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>38.169677734375</v>
+        <v>38.16967391967773</v>
       </c>
       <c r="C59" t="n">
         <v>57.18999862670898</v>
@@ -1690,7 +1690,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>35.16628646850586</v>
+        <v>35.16629791259766</v>
       </c>
       <c r="C60" t="n">
         <v>52.68999862670898</v>
@@ -1740,7 +1740,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>36.76143646240234</v>
+        <v>36.76142883300781</v>
       </c>
       <c r="C62" t="n">
         <v>55.08000183105469</v>
@@ -1765,7 +1765,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>34.25859069824219</v>
+        <v>34.25861740112305</v>
       </c>
       <c r="C63" t="n">
         <v>51.33000183105469</v>
@@ -1794,7 +1794,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>35.67353439331055</v>
+        <v>35.67354583740234</v>
       </c>
       <c r="C64" t="n">
         <v>53.45000076293945</v>
@@ -1823,7 +1823,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>37.94275665283203</v>
+        <v>37.94276809692383</v>
       </c>
       <c r="C65" t="n">
         <v>56.84999847412109</v>
@@ -1852,7 +1852,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>40.40552139282227</v>
+        <v>40.40553283691406</v>
       </c>
       <c r="C66" t="n">
         <v>60.54000091552734</v>
@@ -1881,7 +1881,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>38.94390869140625</v>
+        <v>38.94389343261719</v>
       </c>
       <c r="C67" t="n">
         <v>58.34999847412109</v>
@@ -1910,7 +1910,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>36.50780487060547</v>
+        <v>36.50780868530273</v>
       </c>
       <c r="C68" t="n">
         <v>54.70000076293945</v>
@@ -1939,7 +1939,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>37.17673873901367</v>
+        <v>37.17673492431641</v>
       </c>
       <c r="C69" t="n">
         <v>55.40000152587891</v>
@@ -1968,7 +1968,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>36.88147735595703</v>
+        <v>36.88146591186523</v>
       </c>
       <c r="C70" t="n">
         <v>54.95999908447266</v>
@@ -1997,7 +1997,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>38.43161773681641</v>
+        <v>38.43163299560547</v>
       </c>
       <c r="C71" t="n">
         <v>57.27000045776367</v>
@@ -2026,7 +2026,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>39.05183029174805</v>
+        <v>39.05182647705078</v>
       </c>
       <c r="C72" t="n">
         <v>57.90999984741211</v>
@@ -2084,7 +2084,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>45.80885696411133</v>
+        <v>45.80886459350586</v>
       </c>
       <c r="C74" t="n">
         <v>67.93000030517578</v>
@@ -2113,7 +2113,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>46.10923385620117</v>
+        <v>46.10923004150391</v>
       </c>
       <c r="C75" t="n">
         <v>68.01000213623047</v>
@@ -2142,7 +2142,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>46.08211517333984</v>
+        <v>46.08210754394531</v>
       </c>
       <c r="C76" t="n">
         <v>67.97000122070312</v>
@@ -2171,7 +2171,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>48.2109489440918</v>
+        <v>48.21095657348633</v>
       </c>
       <c r="C77" t="n">
         <v>71.11000061035156</v>
@@ -2229,7 +2229,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>49.68399810791016</v>
+        <v>49.68403244018555</v>
       </c>
       <c r="C79" t="n">
         <v>72.91000366210938</v>
@@ -2258,7 +2258,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>56.28723526000977</v>
+        <v>56.28718948364258</v>
       </c>
       <c r="C80" t="n">
         <v>82.59999847412109</v>
@@ -2287,7 +2287,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>57.43815994262695</v>
+        <v>57.43814086914062</v>
       </c>
       <c r="C81" t="n">
         <v>83.91999816894531</v>
@@ -2316,7 +2316,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>57.6914176940918</v>
+        <v>57.69142913818359</v>
       </c>
       <c r="C82" t="n">
         <v>84.29000091552734</v>
@@ -2374,7 +2374,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>61.03513717651367</v>
+        <v>61.0351676940918</v>
       </c>
       <c r="C84" t="n">
         <v>88.80000305175781</v>
@@ -2403,7 +2403,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>59.24808502197266</v>
+        <v>59.24809646606445</v>
       </c>
       <c r="C85" t="n">
         <v>86.19999694824219</v>
@@ -2461,7 +2461,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>63.26802444458008</v>
+        <v>63.26803970336914</v>
       </c>
       <c r="C87" t="n">
         <v>91.55000305175781</v>
@@ -2490,7 +2490,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>70.84222412109375</v>
+        <v>70.84224700927734</v>
       </c>
       <c r="C88" t="n">
         <v>102.5100021362305</v>
@@ -2519,7 +2519,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>72.01703643798828</v>
+        <v>72.01705169677734</v>
       </c>
       <c r="C89" t="n">
         <v>104.2099990844727</v>
@@ -2548,7 +2548,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>69.78073883056641</v>
+        <v>69.78070831298828</v>
       </c>
       <c r="C90" t="n">
         <v>100.5299987792969</v>
@@ -2577,7 +2577,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>68.48269653320312</v>
+        <v>68.48271942138672</v>
       </c>
       <c r="C91" t="n">
         <v>98.66000366210938</v>
@@ -2606,7 +2606,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>75.16713714599609</v>
+        <v>75.16716003417969</v>
       </c>
       <c r="C92" t="n">
         <v>108.2900009155273</v>
@@ -2635,7 +2635,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>75.94929504394531</v>
+        <v>75.94928741455078</v>
       </c>
       <c r="C93" t="n">
         <v>108.9400024414062</v>
@@ -2722,7 +2722,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>79.86439514160156</v>
+        <v>79.86441802978516</v>
       </c>
       <c r="C96" t="n">
         <v>114.0800018310547</v>
@@ -2751,7 +2751,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>79.86439514160156</v>
+        <v>79.86441802978516</v>
       </c>
       <c r="C97" t="n">
         <v>114.0800018310547</v>
@@ -2780,7 +2780,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>83.27376556396484</v>
+        <v>83.27377319335938</v>
       </c>
       <c r="C98" t="n">
         <v>118.9499969482422</v>
@@ -2809,7 +2809,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>87.26565551757812</v>
+        <v>87.26563262939453</v>
       </c>
       <c r="C99" t="n">
         <v>124.0199966430664</v>
@@ -2838,7 +2838,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>86.78715515136719</v>
+        <v>86.78716278076172</v>
       </c>
       <c r="C100" t="n">
         <v>123.3399963378906</v>
@@ -2896,7 +2896,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>82.06344604492188</v>
+        <v>82.06345367431641</v>
       </c>
       <c r="C102" t="n">
         <v>115.9899978637695</v>
@@ -2925,7 +2925,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>83.74730682373047</v>
+        <v>83.74726104736328</v>
       </c>
       <c r="C103" t="n">
         <v>118.370002746582</v>
@@ -2954,7 +2954,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>90.12899017333984</v>
+        <v>90.12895965576172</v>
       </c>
       <c r="C104" t="n">
         <v>127.3899993896484</v>
@@ -3070,7 +3070,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>117.9696350097656</v>
+        <v>117.9696273803711</v>
       </c>
       <c r="C108" t="n">
         <v>165.3099975585938</v>
@@ -3099,7 +3099,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>113.6735763549805</v>
+        <v>113.6735916137695</v>
       </c>
       <c r="C109" t="n">
         <v>159.2899932861328</v>
@@ -3128,7 +3128,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>108.6568298339844</v>
+        <v>108.6567993164062</v>
       </c>
       <c r="C110" t="n">
         <v>152.2599945068359</v>
@@ -3157,7 +3157,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>113.1491088867188</v>
+        <v>113.1491241455078</v>
       </c>
       <c r="C111" t="n">
         <v>157.7200012207031</v>
@@ -3186,7 +3186,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>114.6771621704102</v>
+        <v>114.6772155761719</v>
       </c>
       <c r="C112" t="n">
         <v>159.8500061035156</v>
@@ -3215,7 +3215,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>113.2853927612305</v>
+        <v>113.2854080200195</v>
       </c>
       <c r="C113" t="n">
         <v>157.9100036621094</v>
@@ -3244,7 +3244,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>112.6542587280273</v>
+        <v>112.6542816162109</v>
       </c>
       <c r="C114" t="n">
         <v>156.2599945068359</v>
@@ -3273,7 +3273,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>110.6789398193359</v>
+        <v>110.6789245605469</v>
       </c>
       <c r="C115" t="n">
         <v>153.5200042724609</v>
@@ -3302,7 +3302,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>127.3110122680664</v>
+        <v>127.3110275268555</v>
       </c>
       <c r="C116" t="n">
         <v>176.5899963378906</v>
@@ -3331,7 +3331,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>109.9335098266602</v>
+        <v>109.9334564208984</v>
       </c>
       <c r="C117" t="n">
         <v>151.7799987792969</v>
@@ -3360,7 +3360,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>100.1844787597656</v>
+        <v>100.184455871582</v>
       </c>
       <c r="C118" t="n">
         <v>138.3200073242188</v>
@@ -3389,7 +3389,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>114.5689697265625</v>
+        <v>114.5689926147461</v>
       </c>
       <c r="C119" t="n">
         <v>158.1799926757812</v>
@@ -3418,7 +3418,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>117.2745590209961</v>
+        <v>117.274543762207</v>
       </c>
       <c r="C120" t="n">
         <v>161.1000061035156</v>
@@ -3447,7 +3447,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>118.1699447631836</v>
+        <v>118.1699066162109</v>
       </c>
       <c r="C121" t="n">
         <v>162.3300018310547</v>
@@ -3476,7 +3476,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>111.181526184082</v>
+        <v>111.1815032958984</v>
       </c>
       <c r="C122" t="n">
         <v>152.7299957275391</v>
@@ -3505,7 +3505,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>104.2945251464844</v>
+        <v>104.2945556640625</v>
       </c>
       <c r="C123" t="n">
         <v>142.2799987792969</v>
@@ -3534,7 +3534,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>109.9021606445312</v>
+        <v>109.9021453857422</v>
       </c>
       <c r="C124" t="n">
         <v>149.9299926757812</v>
@@ -3563,7 +3563,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>116.0375442504883</v>
+        <v>116.0375747680664</v>
       </c>
       <c r="C125" t="n">
         <v>158.3000030517578</v>
@@ -3592,7 +3592,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>116.5432281494141</v>
+        <v>116.5432205200195</v>
       </c>
       <c r="C126" t="n">
         <v>157.9499969482422</v>
@@ -3621,7 +3621,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>112.2636947631836</v>
+        <v>112.2636871337891</v>
       </c>
       <c r="C127" t="n">
         <v>152.1499938964844</v>
@@ -3650,7 +3650,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>126.9321746826172</v>
+        <v>126.93212890625</v>
       </c>
       <c r="C128" t="n">
         <v>172.0299987792969</v>
@@ -3679,7 +3679,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>126.2080535888672</v>
+        <v>126.2080230712891</v>
       </c>
       <c r="C129" t="n">
         <v>170.0599975585938</v>
@@ -3708,7 +3708,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>123.7960662841797</v>
+        <v>123.7960739135742</v>
       </c>
       <c r="C130" t="n">
         <v>166.8099975585938</v>
@@ -3737,7 +3737,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>104.7602615356445</v>
+        <v>104.76025390625</v>
       </c>
       <c r="C131" t="n">
         <v>141.1600036621094</v>
@@ -3766,7 +3766,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>107.6421127319336</v>
+        <v>107.64208984375</v>
       </c>
       <c r="C132" t="n">
         <v>144.0700073242188</v>
@@ -3824,7 +3824,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>117.0636596679688</v>
+        <v>117.0636672973633</v>
       </c>
       <c r="C134" t="n">
         <v>156.6799926757812</v>
@@ -3882,7 +3882,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>123.4305877685547</v>
+        <v>123.4305725097656</v>
       </c>
       <c r="C136" t="n">
         <v>164.0700073242188</v>
@@ -3911,7 +3911,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>122.8663558959961</v>
+        <v>122.8663711547852</v>
       </c>
       <c r="C137" t="n">
         <v>163.3200073242188</v>
@@ -3940,7 +3940,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>117.632080078125</v>
+        <v>117.6320266723633</v>
       </c>
       <c r="C138" t="n">
         <v>155.2400054931641</v>
@@ -3969,7 +3969,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>130.5060729980469</v>
+        <v>130.5060882568359</v>
       </c>
       <c r="C139" t="n">
         <v>172.2299957275391</v>
@@ -3998,7 +3998,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>132.2337341308594</v>
+        <v>132.2337188720703</v>
       </c>
       <c r="C140" t="n">
         <v>174.5099945068359</v>
@@ -4027,7 +4027,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>135.6125030517578</v>
+        <v>135.6124572753906</v>
       </c>
       <c r="C141" t="n">
         <v>177.7700042724609</v>
@@ -4056,7 +4056,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>142.2340087890625</v>
+        <v>142.2339782714844</v>
       </c>
       <c r="C142" t="n">
         <v>186.4499969482422</v>
@@ -4114,7 +4114,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>134.9188232421875</v>
+        <v>134.9188842773438</v>
       </c>
       <c r="C144" t="n">
         <v>175.6600036621094</v>
@@ -4143,7 +4143,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>133.5670623779297</v>
+        <v>133.5670318603516</v>
       </c>
       <c r="C145" t="n">
         <v>173.8999938964844</v>
@@ -4172,7 +4172,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>142.8991241455078</v>
+        <v>142.8991088867188</v>
       </c>
       <c r="C146" t="n">
         <v>186.0500030517578</v>
@@ -4230,7 +4230,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>131.9300537109375</v>
+        <v>131.9300842285156</v>
       </c>
       <c r="C148" t="n">
         <v>170.4799957275391</v>
@@ -4259,7 +4259,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>135.025634765625</v>
+        <v>135.0256042480469</v>
       </c>
       <c r="C149" t="n">
         <v>174.4799957275391</v>
@@ -4288,7 +4288,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>140.076171875</v>
+        <v>140.0762023925781</v>
       </c>
       <c r="C150" t="n">
         <v>179.6199951171875</v>
@@ -4317,7 +4317,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>143.9520416259766</v>
+        <v>143.9519958496094</v>
       </c>
       <c r="C151" t="n">
         <v>184.5899963378906</v>
@@ -4346,7 +4346,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>153.2790222167969</v>
+        <v>153.2789916992188</v>
       </c>
       <c r="C152" t="n">
         <v>196.5500030517578</v>
@@ -4375,7 +4375,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>156.8818511962891</v>
+        <v>156.8818664550781</v>
       </c>
       <c r="C153" t="n">
         <v>199.8099975585938</v>
@@ -4404,7 +4404,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>162.7548217773438</v>
+        <v>162.7547760009766</v>
       </c>
       <c r="C154" t="n">
         <v>207.2899932861328</v>
@@ -4433,7 +4433,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>151.3700866699219</v>
+        <v>151.3700561523438</v>
       </c>
       <c r="C155" t="n">
         <v>192.7899932861328</v>
@@ -4462,7 +4462,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>164.6503143310547</v>
+        <v>164.6502838134766</v>
       </c>
       <c r="C156" t="n">
         <v>208.25</v>
@@ -4491,7 +4491,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>153.9134521484375</v>
+        <v>153.9134368896484</v>
       </c>
       <c r="C157" t="n">
         <v>194.6699981689453</v>
@@ -4520,7 +4520,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>147.9361724853516</v>
+        <v>147.9362030029297</v>
       </c>
       <c r="C158" t="n">
         <v>187.1100006103516</v>
@@ -4549,7 +4549,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>151.4464263916016</v>
+        <v>151.4464111328125</v>
       </c>
       <c r="C159" t="n">
         <v>190.0800018310547</v>
@@ -4578,7 +4578,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>151.3667144775391</v>
+        <v>151.3667297363281</v>
       </c>
       <c r="C160" t="n">
         <v>189.9799957275391</v>
@@ -4607,7 +4607,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>142.8734130859375</v>
+        <v>142.8733673095703</v>
       </c>
       <c r="C161" t="n">
         <v>179.3200073242188</v>
@@ -4665,7 +4665,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>148.0893402099609</v>
+        <v>148.0893249511719</v>
       </c>
       <c r="C163" t="n">
         <v>184.2799987792969</v>
@@ -4694,7 +4694,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>149.9376373291016</v>
+        <v>149.9376678466797</v>
       </c>
       <c r="C164" t="n">
         <v>186.5800018310547</v>
@@ -4781,7 +4781,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>172.583984375</v>
+        <v>172.5840301513672</v>
       </c>
       <c r="C167" t="n">
         <v>213.25</v>
@@ -4810,7 +4810,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>191.2219390869141</v>
+        <v>191.2219543457031</v>
       </c>
       <c r="C168" t="n">
         <v>234.7200012207031</v>
@@ -4839,7 +4839,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>196.3952026367188</v>
+        <v>196.3951873779297</v>
       </c>
       <c r="C169" t="n">
         <v>241.0700073242188</v>
@@ -4868,7 +4868,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>176.0118865966797</v>
+        <v>176.0119018554688</v>
       </c>
       <c r="C170" t="n">
         <v>216.0500030517578</v>
@@ -4897,7 +4897,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>163.871337890625</v>
+        <v>163.8713073730469</v>
       </c>
       <c r="C171" t="n">
         <v>199.7299957275391</v>
@@ -4926,7 +4926,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>166.3327484130859</v>
+        <v>166.3327026367188</v>
       </c>
       <c r="C172" t="n">
         <v>202.7299957275391</v>
@@ -4955,7 +4955,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>196.2714538574219</v>
+        <v>196.2714691162109</v>
       </c>
       <c r="C173" t="n">
         <v>239.2200012207031</v>
@@ -5013,7 +5013,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>194.8245391845703</v>
+        <v>194.8245544433594</v>
       </c>
       <c r="C175" t="n">
         <v>235.8600006103516</v>
@@ -5042,7 +5042,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>202.1017913818359</v>
+        <v>202.1017456054688</v>
       </c>
       <c r="C176" t="n">
         <v>244.6699981689453</v>
@@ -5071,7 +5071,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>210.6484527587891</v>
+        <v>210.6484375</v>
       </c>
       <c r="C177" t="n">
         <v>253.3200073242188</v>
@@ -5100,7 +5100,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>211.3469543457031</v>
+        <v>211.3469390869141</v>
       </c>
       <c r="C178" t="n">
         <v>254.1600036621094</v>
@@ -5129,7 +5129,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>180.3966217041016</v>
+        <v>180.3966369628906</v>
       </c>
       <c r="C179" t="n">
         <v>216.9400024414062</v>
@@ -5187,7 +5187,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>192.4889068603516</v>
+        <v>192.4888916015625</v>
       </c>
       <c r="C181" t="n">
         <v>229.9199981689453</v>
@@ -5216,7 +5216,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>202.1250457763672</v>
+        <v>202.1250305175781</v>
       </c>
       <c r="C182" t="n">
         <v>241.4299926757812</v>
@@ -5245,7 +5245,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>189.7030334472656</v>
+        <v>189.7030181884766</v>
       </c>
       <c r="C183" t="n">
         <v>224.9199981689453</v>
@@ -5274,7 +5274,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>209.8524475097656</v>
+        <v>209.8524322509766</v>
       </c>
       <c r="C184" t="n">
         <v>248.8099975585938</v>
@@ -5303,7 +5303,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>202.1181945800781</v>
+        <v>202.1182403564453</v>
       </c>
       <c r="C185" t="n">
         <v>239.6399993896484</v>
@@ -5332,7 +5332,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>202.0955047607422</v>
+        <v>202.0955200195312</v>
       </c>
       <c r="C186" t="n">
         <v>237.9400024414062</v>
@@ -5361,7 +5361,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>207.0302734375</v>
+        <v>207.0302276611328</v>
       </c>
       <c r="C187" t="n">
         <v>243.75</v>
@@ -5419,7 +5419,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>193.0342254638672</v>
+        <v>193.0341949462891</v>
       </c>
       <c r="C189" t="n">
         <v>225.5299987792969</v>
@@ -5448,7 +5448,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>182.010009765625</v>
+        <v>182.0100250244141</v>
       </c>
       <c r="C190" t="n">
         <v>212.6499938964844</v>
@@ -5477,7 +5477,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>177.1484375</v>
+        <v>177.1484527587891</v>
       </c>
       <c r="C191" t="n">
         <v>206.9700012207031</v>
@@ -5535,7 +5535,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>194.1715087890625</v>
+        <v>194.1715240478516</v>
       </c>
       <c r="C193" t="n">
         <v>224.9700012207031</v>
@@ -5564,7 +5564,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>196.0444488525391</v>
+        <v>196.0444641113281</v>
       </c>
       <c r="C194" t="n">
         <v>227.1399993896484</v>
@@ -5651,7 +5651,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>202.9918823242188</v>
+        <v>202.9918975830078</v>
       </c>
       <c r="C197" t="n">
         <v>233.1900024414062</v>
@@ -5680,7 +5680,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>225.2877960205078</v>
+        <v>225.2877807617188</v>
       </c>
       <c r="C198" t="n">
         <v>256.739990234375</v>
@@ -5709,7 +5709,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>213.4942779541016</v>
+        <v>213.4942932128906</v>
       </c>
       <c r="C199" t="n">
         <v>243.3000030517578</v>
@@ -5738,7 +5738,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>217.1533966064453</v>
+        <v>217.1534271240234</v>
       </c>
       <c r="C200" t="n">
         <v>247.4700012207031</v>
@@ -5767,7 +5767,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>212.4902038574219</v>
+        <v>212.4902191162109</v>
       </c>
       <c r="C201" t="n">
         <v>240.3000030517578</v>
@@ -5796,7 +5796,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>199.3145599365234</v>
+        <v>199.3145751953125</v>
       </c>
       <c r="C202" t="n">
         <v>225.3999938964844</v>
@@ -5825,7 +5825,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>239.0625152587891</v>
+        <v>239.0625</v>
       </c>
       <c r="C203" t="n">
         <v>270.3500061035156</v>
@@ -5883,7 +5883,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>233.8444671630859</v>
+        <v>233.8444366455078</v>
       </c>
       <c r="C205" t="n">
         <v>262.6400146484375</v>
@@ -5941,7 +5941,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>208.0800476074219</v>
+        <v>208.0800323486328</v>
       </c>
       <c r="C207" t="n">
         <v>231.6600036621094</v>
@@ -5970,7 +5970,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>217.1430053710938</v>
+        <v>217.1429748535156</v>
       </c>
       <c r="C208" t="n">
         <v>241.75</v>
@@ -5999,7 +5999,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>215.3376007080078</v>
+        <v>215.3375854492188</v>
       </c>
       <c r="C209" t="n">
         <v>239.7400054931641</v>
@@ -6028,7 +6028,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>200.0606536865234</v>
+        <v>200.0606842041016</v>
       </c>
       <c r="C210" t="n">
         <v>220.6499938964844</v>
@@ -6057,7 +6057,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>201.3028259277344</v>
+        <v>201.3028106689453</v>
       </c>
       <c r="C211" t="n">
         <v>222.0200042724609</v>
@@ -6086,7 +6086,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>212.3009490966797</v>
+        <v>212.3009643554688</v>
       </c>
       <c r="C212" t="n">
         <v>234.1499938964844</v>
@@ -6115,7 +6115,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>234.3034820556641</v>
+        <v>234.3035278320312</v>
       </c>
       <c r="C213" t="n">
         <v>256.3399963378906</v>
@@ -6144,7 +6144,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>245.6557922363281</v>
+        <v>245.6558074951172</v>
       </c>
       <c r="C214" t="n">
         <v>268.760009765625</v>
@@ -6173,7 +6173,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>233.7185211181641</v>
+        <v>233.718505859375</v>
       </c>
       <c r="C215" t="n">
         <v>255.6999969482422</v>
@@ -6202,7 +6202,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>248.3979949951172</v>
+        <v>248.3980407714844</v>
       </c>
       <c r="C216" t="n">
         <v>269.6400146484375</v>
@@ -6231,7 +6231,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>265.3300476074219</v>
+        <v>265.3300170898438</v>
       </c>
       <c r="C217" t="n">
         <v>288.0199890136719</v>
@@ -6260,7 +6260,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>289.5028381347656</v>
+        <v>289.5028991699219</v>
       </c>
       <c r="C218" t="n">
         <v>314.260009765625</v>
@@ -6289,7 +6289,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>254.2299041748047</v>
+        <v>254.2298889160156</v>
       </c>
       <c r="C219" t="n">
         <v>273.8299865722656</v>
@@ -6318,7 +6318,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>263.9691162109375</v>
+        <v>263.9690856933594</v>
       </c>
       <c r="C220" t="n">
         <v>284.3200073242188</v>
@@ -6347,7 +6347,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>254.3320465087891</v>
+        <v>254.33203125</v>
       </c>
       <c r="C221" t="n">
         <v>273.9400024414062</v>
@@ -6376,7 +6376,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>285.9747924804688</v>
+        <v>285.9748229980469</v>
       </c>
       <c r="C222" t="n">
         <v>305.8500061035156</v>
@@ -6405,7 +6405,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>292.14599609375</v>
+        <v>292.1459350585938</v>
       </c>
       <c r="C223" t="n">
         <v>312.4500122070312</v>
@@ -6434,7 +6434,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>310.8649597167969</v>
+        <v>310.8650207519531</v>
       </c>
       <c r="C224" t="n">
         <v>332.4700012207031</v>
@@ -6521,7 +6521,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>301.4392700195312</v>
+        <v>301.4393005371094</v>
       </c>
       <c r="C227" t="n">
         <v>320.1600036621094</v>
@@ -6550,7 +6550,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>268.4595336914062</v>
+        <v>268.4595642089844</v>
       </c>
       <c r="C228" t="n">
         <v>282.8699951171875</v>
@@ -6579,7 +6579,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>247.3620452880859</v>
+        <v>247.362060546875</v>
       </c>
       <c r="C229" t="n">
         <v>260.6400146484375</v>
@@ -6666,7 +6666,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>298.0672302246094</v>
+        <v>298.0672912597656</v>
       </c>
       <c r="C232" t="n">
         <v>311.5499877929688</v>
@@ -6695,7 +6695,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>278.330078125</v>
+        <v>278.3300476074219</v>
       </c>
       <c r="C233" t="n">
         <v>290.9200134277344</v>
@@ -6724,7 +6724,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>278.1452026367188</v>
+        <v>278.1451721191406</v>
       </c>
       <c r="C234" t="n">
         <v>288.1799926757812</v>
@@ -6811,7 +6811,7 @@
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>279.9442443847656</v>
+        <v>279.9442749023438</v>
       </c>
       <c r="C237" t="n">
         <v>287.7099914550781</v>
@@ -6840,7 +6840,7 @@
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>274.5830383300781</v>
+        <v>274.5830078125</v>
       </c>
       <c r="C238" t="n">
         <v>282.2000122070312</v>
@@ -6869,7 +6869,7 @@
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>290.3749389648438</v>
+        <v>290.3748779296875</v>
       </c>
       <c r="C239" t="n">
         <v>298.4299926757812</v>
@@ -6898,7 +6898,7 @@
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>338.5329895019531</v>
+        <v>338.532958984375</v>
       </c>
       <c r="C240" t="n">
         <v>345.4599914550781</v>
